--- a/artfynd/A 54028-2020 artfynd.xlsx
+++ b/artfynd/A 54028-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54028-2020 artfynd.xlsx
+++ b/artfynd/A 54028-2020 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>69624119</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461864.7703255828</v>
+        <v>461865</v>
       </c>
       <c r="R5" t="n">
-        <v>6793135.949623086</v>
+        <v>6793136</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1084,9 @@
           <t>2017-06-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-06-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54028-2020 artfynd.xlsx
+++ b/artfynd/A 54028-2020 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>69624119</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
